--- a/Employee_Reports_wi48/Sathis Gunawardhana Dikella Kandha Yakdhehirallage Q0572.xlsx
+++ b/Employee_Reports_wi48/Sathis Gunawardhana Dikella Kandha Yakdhehirallage Q0572.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1608,11 +1608,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1657,11 +1657,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1680,9 +1680,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
           <t>29-Jan-2026</t>
@@ -1694,11 +1706,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1743,11 +1755,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1792,11 +1804,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1841,11 +1853,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -1890,11 +1902,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1927,11 +1939,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -1964,11 +1976,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -2001,11 +2013,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2050,11 +2062,11 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2099,11 +2111,11 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2148,11 +2160,11 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -2185,11 +2197,11 @@
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2620,7 +2632,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2649,7 +2661,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2678,7 +2690,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7938</v>
+        <v>7935</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2707,7 +2719,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2736,7 +2748,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2777,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7938</v>
+        <v>7935</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2794,7 +2806,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7982</v>
+        <v>7979</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2823,7 +2835,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7982</v>
+        <v>7979</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2852,7 +2864,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2881,7 +2893,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2910,7 +2922,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7982</v>
+        <v>7979</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2939,7 +2951,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7982</v>
+        <v>7979</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2968,7 +2980,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7982</v>
+        <v>7979</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2997,7 +3009,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7982</v>
+        <v>7979</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -3026,7 +3038,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -3055,7 +3067,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
